--- a/Bond.xlsx
+++ b/Bond.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://marinercapital-my.sharepoint.com/personal/pgazzano_marinercapital_com/Documents/Attachments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1470" documentId="8_{D5AC41B5-B0A9-4002-941A-1D8535AA3FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{960AEB21-9D78-411F-9D19-AAF53A55D9EA}"/>
+  <xr:revisionPtr revIDLastSave="320" documentId="6_{217F19BB-6356-472C-81B3-D4A79A7F18E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB4649C5-0B5B-4E83-B5AA-EDA8554C4131}"/>
   <bookViews>
-    <workbookView xWindow="20880" yWindow="1605" windowWidth="37335" windowHeight="16095" tabRatio="718" xr2:uid="{C448CA47-130C-4FDA-ADE2-BAEF8A55A592}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21840" tabRatio="718" xr2:uid="{C448CA47-130C-4FDA-ADE2-BAEF8A55A592}"/>
   </bookViews>
   <sheets>
     <sheet name="USD Curve" sheetId="10" r:id="rId1"/>
@@ -44,7 +44,7 @@
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1" iterateCount="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -87,28 +87,19 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>SOFRSWAP</t>
+    <t>czb2a6</t>
   </si>
   <si>
-    <t>EURIBORSWAP</t>
-  </si>
-  <si>
-    <t>qwSwapDiscountCurve($A$2,AH30)</t>
-  </si>
-  <si>
-    <t>qwSwapDis\countCurve($A$2,AH31)</t>
-  </si>
-  <si>
-    <t>qwSwapDiscountCurve($A$2,AH32)</t>
+    <t>SP 06/30/27 Govt</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="12">
+  <numFmts count="15">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.000000%"/>
@@ -121,8 +112,11 @@
     <numFmt numFmtId="172" formatCode="0.00000000%"/>
     <numFmt numFmtId="173" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="174" formatCode="0.0000000"/>
+    <numFmt numFmtId="175" formatCode="_(* #,##0.0000000_);_(* \(#,##0.0000000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0.000000000_);_(* \(#,##0.000000000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_(* #,##0.00000_);_(* \(#,##0.00000\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -133,6 +127,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -160,7 +160,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -179,6 +179,13 @@
     <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -527,27 +534,28 @@
   <dimension ref="A1:AK114"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.140625" customWidth="1"/>
     <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.42578125" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="12.85546875" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="11.5703125" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="13.85546875" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="14.28515625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="12.140625" customWidth="1"/>
-    <col min="13" max="13" width="14" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="255.5703125" customWidth="1"/>
+    <col min="11" max="13" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.28515625" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="2" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="21.140625" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="24.85546875" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="12" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="13.7109375" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="0" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="9.140625" hidden="1" customWidth="1"/>
     <col min="20" max="20" width="15" hidden="1" customWidth="1"/>
-    <col min="21" max="22" width="0" hidden="1" customWidth="1"/>
-    <col min="24" max="24" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="19.140625" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="18.85546875" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="20.5703125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="21.42578125" bestFit="1" customWidth="1"/>
@@ -560,13 +568,12 @@
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" t="str" cm="1">
         <f t="array" ref="A2">_xll.qwCtxTrade()</f>
-        <v>ctx.46150.Live</v>
+        <v>ctx.46192.Close</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" cm="1">
-        <f t="array" ref="A3">_xll.qwCtxDate(A2)</f>
-        <v>46150</v>
+      <c r="A3" s="2" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
@@ -619,12 +626,6 @@
       <c r="C12" s="2"/>
       <c r="J12" s="2"/>
       <c r="Q12" s="2"/>
-      <c r="X12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>1</v>
-      </c>
       <c r="Z12" s="3"/>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.25">
@@ -644,42 +645,27 @@
     <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C15" s="8"/>
       <c r="E15" s="10"/>
-      <c r="I15" s="2"/>
+      <c r="I15" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="J15" s="2"/>
       <c r="Q15" s="2"/>
-      <c r="X15" t="str" cm="1">
-        <f t="array" ref="X15:X44">_xll.qwCurveBenchmarks(A2,X12)</f>
-        <v>USOSFR1Z</v>
-      </c>
-      <c r="Y15" cm="1">
-        <f t="array" ref="Y15">_xll.qwYield($A$2,X15,0)</f>
-        <v>3.6282349999999998E-2</v>
-      </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
+      <c r="K16" s="11"/>
       <c r="Q16" s="2"/>
-      <c r="X16" t="str">
-        <v>USOSFR2Z</v>
-      </c>
-      <c r="Y16" cm="1">
-        <f t="array" ref="Y16">_xll.qwYield($A$2,X16,0)</f>
-        <v>3.6237999999999999E-2</v>
-      </c>
     </row>
     <row r="17" spans="3:37" x14ac:dyDescent="0.25">
       <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
+      <c r="J17" s="22" t="e" cm="1">
+        <f t="array" ref="J17">_xll.qwPrice(A2,I15)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="K17" s="20"/>
       <c r="Q17" s="2"/>
-      <c r="X17" t="str">
-        <v>USOSFR3Z</v>
-      </c>
-      <c r="Y17" cm="1">
-        <f t="array" ref="Y17">_xll.qwYield($A$2,X17,0)</f>
-        <v>3.6318049999999998E-2</v>
-      </c>
     </row>
     <row r="18" spans="3:37" x14ac:dyDescent="0.25">
       <c r="C18" s="2"/>
@@ -687,146 +673,170 @@
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="Q18" s="2"/>
-      <c r="X18" t="str">
-        <v>USOSFRA</v>
-      </c>
-      <c r="Y18" cm="1">
-        <f t="array" ref="Y18">_xll.qwYield($A$2,X18,0)</f>
-        <v>3.6326399999999995E-2</v>
-      </c>
     </row>
     <row r="19" spans="3:37" x14ac:dyDescent="0.25">
       <c r="C19" s="2"/>
       <c r="D19" s="9"/>
       <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
+      <c r="J19" s="2" t="str" cm="1">
+        <f t="array" ref="J19:J28">_xll.qwBlmRequests(A2)</f>
+        <v>SendRequest (1) IntradayBarRequest = {_x000D_
+    security = "SP 06/30/27 GOVT"_x000D_
+    eventType = BID_x000D_
+    startDateTime = 2026-06-24T09:00:00.000_x000D_
+    endDateTime = 2026-06-24T19:00:00.000_x000D_
+    interval = 600_x000D_
+    gapFillInitialBar = true_x000D_
+}_x000D_
+ m_numRequests: 1</v>
+      </c>
+      <c r="K19" s="18"/>
       <c r="Q19" s="2"/>
-      <c r="X19" t="str">
-        <v>USOSFRB</v>
-      </c>
-      <c r="Y19" cm="1">
-        <f t="array" ref="Y19">_xll.qwYield($A$2,X19,0)</f>
-        <v>3.6394249999999996E-2</v>
-      </c>
     </row>
     <row r="20" spans="3:37" x14ac:dyDescent="0.25">
       <c r="C20" s="2"/>
       <c r="E20" s="8"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
+      <c r="J20" s="2" t="str">
+        <v>SendRequest (2) IntradayBarRequest = {_x000D_
+    security = "SP 06/30/27 GOVT"_x000D_
+    eventType = ASK_x000D_
+    startDateTime = 2026-06-24T09:00:00.000_x000D_
+    endDateTime = 2026-06-24T19:00:00.000_x000D_
+    interval = 600_x000D_
+    gapFillInitialBar = true_x000D_
+}_x000D_
+ m_numRequests: 2</v>
+      </c>
       <c r="Q20" s="2"/>
-      <c r="X20" t="str">
-        <v>USOSFRC</v>
-      </c>
-      <c r="Y20" cm="1">
-        <f t="array" ref="Y20">_xll.qwYield($A$2,X20,0)</f>
-        <v>3.6443799999999998E-2</v>
-      </c>
     </row>
     <row r="21" spans="3:37" x14ac:dyDescent="0.25">
       <c r="C21" s="2"/>
       <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
+      <c r="J21" s="2" t="str">
+        <v>SendRequest (3) IntradayBarRequest = {_x000D_
+    security = "SP 06/30/27 GOVT"_x000D_
+    eventType = BID_x000D_
+    startDateTime = 2026-06-23T09:00:00.000_x000D_
+    endDateTime = 2026-06-23T19:00:00.000_x000D_
+    interval = 600_x000D_
+    gapFillInitialBar = true_x000D_
+}_x000D_
+ m_numRequests: 3</v>
+      </c>
       <c r="Q21" s="2"/>
-      <c r="X21" t="str">
-        <v>USOSFRD</v>
-      </c>
-      <c r="Y21" cm="1">
-        <f t="array" ref="Y21">_xll.qwYield($A$2,X21,0)</f>
-        <v>3.6481449999999999E-2</v>
-      </c>
     </row>
     <row r="22" spans="3:37" x14ac:dyDescent="0.25">
       <c r="C22" s="2"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
+      <c r="J22" s="2" t="str">
+        <v>SendRequest (4) IntradayBarRequest = {_x000D_
+    security = "SP 06/30/27 GOVT"_x000D_
+    eventType = ASK_x000D_
+    startDateTime = 2026-06-23T09:00:00.000_x000D_
+    endDateTime = 2026-06-23T19:00:00.000_x000D_
+    interval = 600_x000D_
+    gapFillInitialBar = true_x000D_
+}_x000D_
+ m_numRequests: 4</v>
+      </c>
       <c r="Q22" s="2"/>
-      <c r="X22" t="str">
-        <v>USOSFRE</v>
-      </c>
-      <c r="Y22" cm="1">
-        <f t="array" ref="Y22">_xll.qwYield($A$2,X22,0)</f>
-        <v>3.6544900000000005E-2</v>
-      </c>
     </row>
     <row r="23" spans="3:37" x14ac:dyDescent="0.25">
       <c r="C23" s="2"/>
       <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
+      <c r="J23" s="2" t="str">
+        <v>SendRequest (5) IntradayBarRequest = {_x000D_
+    security = "SP 06/30/27 GOVT"_x000D_
+    eventType = BID_x000D_
+    startDateTime = 2026-06-25T09:00:00.000_x000D_
+    endDateTime = 2026-06-25T19:00:00.000_x000D_
+    interval = 600_x000D_
+    gapFillInitialBar = true_x000D_
+}_x000D_
+ m_numRequests: 5</v>
+      </c>
       <c r="Q23" s="2"/>
-      <c r="X23" t="str">
-        <v>USOSFRF</v>
-      </c>
-      <c r="Y23" cm="1">
-        <f t="array" ref="Y23">_xll.qwYield($A$2,X23,0)</f>
-        <v>3.6623250000000003E-2</v>
-      </c>
     </row>
     <row r="24" spans="3:37" x14ac:dyDescent="0.25">
       <c r="C24" s="2"/>
       <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
+      <c r="J24" s="2" t="str">
+        <v>SendRequest (6) IntradayBarRequest = {_x000D_
+    security = "SP 06/30/27 GOVT"_x000D_
+    eventType = ASK_x000D_
+    startDateTime = 2026-06-25T09:00:00.000_x000D_
+    endDateTime = 2026-06-25T19:00:00.000_x000D_
+    interval = 600_x000D_
+    gapFillInitialBar = true_x000D_
+}_x000D_
+ m_numRequests: 6</v>
+      </c>
       <c r="Q24" s="2"/>
-      <c r="X24" t="str">
-        <v>USOSFRG</v>
-      </c>
-      <c r="Y24" cm="1">
-        <f t="array" ref="Y24">_xll.qwYield($A$2,X24,0)</f>
-        <v>3.6723550000000001E-2</v>
-      </c>
     </row>
     <row r="25" spans="3:37" x14ac:dyDescent="0.25">
       <c r="C25" s="2"/>
       <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
+      <c r="J25" s="2" t="str">
+        <v>SendRequest (7) IntradayBarRequest = {_x000D_
+    security = "SP 06/30/27 GOVT"_x000D_
+    eventType = BID_x000D_
+    startDateTime = 2026-06-22T09:00:00.000_x000D_
+    endDateTime = 2026-06-22T19:00:00.000_x000D_
+    interval = 600_x000D_
+    gapFillInitialBar = true_x000D_
+}_x000D_
+ m_numRequests: 7</v>
+      </c>
       <c r="Q25" s="2"/>
-      <c r="X25" t="str">
-        <v>USOSFRH</v>
-      </c>
-      <c r="Y25" cm="1">
-        <f t="array" ref="Y25">_xll.qwYield($A$2,X25,0)</f>
-        <v>3.6852999999999997E-2</v>
-      </c>
     </row>
     <row r="26" spans="3:37" x14ac:dyDescent="0.25">
       <c r="C26" s="2"/>
       <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
+      <c r="J26" s="2" t="str">
+        <v>SendRequest (8) IntradayBarRequest = {_x000D_
+    security = "SP 06/30/27 GOVT"_x000D_
+    eventType = ASK_x000D_
+    startDateTime = 2026-06-22T09:00:00.000_x000D_
+    endDateTime = 2026-06-22T19:00:00.000_x000D_
+    interval = 600_x000D_
+    gapFillInitialBar = true_x000D_
+}_x000D_
+ m_numRequests: 8</v>
+      </c>
       <c r="Q26" s="2"/>
-      <c r="X26" t="str">
-        <v>USOSFRI</v>
-      </c>
-      <c r="Y26" cm="1">
-        <f t="array" ref="Y26">_xll.qwYield($A$2,X26,0)</f>
-        <v>3.6956749999999997E-2</v>
-      </c>
     </row>
     <row r="27" spans="3:37" x14ac:dyDescent="0.25">
       <c r="C27" s="2"/>
       <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
+      <c r="J27" s="2" t="str">
+        <v>SendRequest (9) IntradayBarRequest = {_x000D_
+    security = "SP 06/30/27 GOVT"_x000D_
+    eventType = BID_x000D_
+    startDateTime = 2026-06-19T09:00:00.000_x000D_
+    endDateTime = 2026-06-19T19:00:00.000_x000D_
+    interval = 600_x000D_
+    gapFillInitialBar = true_x000D_
+}_x000D_
+ m_numRequests: 9</v>
+      </c>
       <c r="Q27" s="2"/>
-      <c r="X27" t="str">
-        <v>USOSFRJ</v>
-      </c>
-      <c r="Y27" cm="1">
-        <f t="array" ref="Y27">_xll.qwYield($A$2,X27,0)</f>
-        <v>3.7050100000000002E-2</v>
-      </c>
       <c r="AI27" s="3"/>
     </row>
     <row r="28" spans="3:37" x14ac:dyDescent="0.25">
       <c r="C28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
+      <c r="J28" s="2" t="str">
+        <v>SendRequest (10) IntradayBarRequest = {_x000D_
+    security = "SP 06/30/27 GOVT"_x000D_
+    eventType = ASK_x000D_
+    startDateTime = 2026-06-19T09:00:00.000_x000D_
+    endDateTime = 2026-06-19T19:00:00.000_x000D_
+    interval = 600_x000D_
+    gapFillInitialBar = true_x000D_
+}_x000D_
+ m_numRequests: 10</v>
+      </c>
       <c r="Q28" s="2"/>
-      <c r="X28" s="3" t="str">
-        <v>USOSFRK</v>
-      </c>
-      <c r="Y28" cm="1">
-        <f t="array" ref="Y28">_xll.qwYield($A$2,X28,0)</f>
-        <v>3.7173100000000001E-2</v>
-      </c>
+      <c r="X28" s="3"/>
       <c r="AI28" s="3"/>
     </row>
     <row r="29" spans="3:37" x14ac:dyDescent="0.25">
@@ -834,13 +844,7 @@
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="Q29" s="2"/>
-      <c r="X29" s="3" t="str">
-        <v>USOSFR1</v>
-      </c>
-      <c r="Y29" cm="1">
-        <f t="array" ref="Y29">_xll.qwYield($A$2,X29,0)</f>
-        <v>3.7288699999999994E-2</v>
-      </c>
+      <c r="X29" s="3"/>
       <c r="AI29" s="3"/>
     </row>
     <row r="30" spans="3:37" x14ac:dyDescent="0.25">
@@ -848,42 +852,29 @@
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="Q30" s="2"/>
-      <c r="X30" s="3" t="str">
-        <v>USOSFR1F</v>
-      </c>
-      <c r="Y30" cm="1">
-        <f t="array" ref="Y30">_xll.qwYield($A$2,X30,0)</f>
-        <v>3.7339150000000002E-2</v>
-      </c>
-      <c r="AI30" s="14" t="s">
-        <v>2</v>
-      </c>
+      <c r="X30" s="3"/>
+      <c r="AI30" s="14"/>
     </row>
     <row r="31" spans="3:37" x14ac:dyDescent="0.25">
       <c r="C31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="Q31" s="2"/>
-      <c r="X31" s="3" t="str">
-        <v>USOSFR2</v>
-      </c>
+      <c r="X31" s="3"/>
       <c r="Y31" s="3"/>
-      <c r="AI31" s="14" t="s">
-        <v>3</v>
-      </c>
+      <c r="AI31" s="14"/>
     </row>
     <row r="32" spans="3:37" x14ac:dyDescent="0.25">
       <c r="C32" s="2"/>
-      <c r="I32" s="2"/>
+      <c r="I32" s="2" t="str" cm="1">
+        <f t="array" ref="I32">_xll.qwBlmSubscriptions(I15)</f>
+        <v>Subscribe [SP 06/30/27 GOVT?fields=ASK,BID&amp;interval=0.1 CorrelationID = {User: SP 06/30/27 GOVT}]</v>
+      </c>
       <c r="J32" s="2"/>
       <c r="Q32" s="2"/>
-      <c r="X32" s="3" t="str">
-        <v>USOSFR3</v>
-      </c>
+      <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
-      <c r="AI32" s="14" t="s">
-        <v>4</v>
-      </c>
+      <c r="AI32" s="14"/>
       <c r="AK32" s="2"/>
     </row>
     <row r="33" spans="3:37" x14ac:dyDescent="0.25">
@@ -891,9 +882,7 @@
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="Q33" s="2"/>
-      <c r="X33" s="3" t="str">
-        <v>USOSFR4</v>
-      </c>
+      <c r="X33" s="3"/>
       <c r="Y33" s="3"/>
       <c r="AI33" s="3"/>
       <c r="AK33" s="2"/>
@@ -903,9 +892,7 @@
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="Q34" s="2"/>
-      <c r="X34" s="3" t="str">
-        <v>USOSFR5</v>
-      </c>
+      <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
       <c r="AI34" s="3"/>
     </row>
@@ -914,9 +901,7 @@
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="Q35" s="2"/>
-      <c r="X35" s="3" t="str">
-        <v>USOSFR6</v>
-      </c>
+      <c r="X35" s="3"/>
       <c r="Y35" s="3"/>
       <c r="AI35" s="3"/>
     </row>
@@ -925,9 +910,7 @@
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="Q36" s="2"/>
-      <c r="X36" s="3" t="str">
-        <v>USOSFR7</v>
-      </c>
+      <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
       <c r="AI36" s="3"/>
     </row>
@@ -936,9 +919,7 @@
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="Q37" s="2"/>
-      <c r="X37" s="3" t="str">
-        <v>USOSFR8</v>
-      </c>
+      <c r="X37" s="3"/>
       <c r="Y37" s="3"/>
       <c r="AI37" s="3"/>
     </row>
@@ -947,9 +928,7 @@
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="Q38" s="2"/>
-      <c r="X38" s="3" t="str">
-        <v>USOSFR9</v>
-      </c>
+      <c r="X38" s="3"/>
       <c r="Y38" s="3"/>
       <c r="AI38" s="3"/>
     </row>
@@ -958,9 +937,7 @@
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="Q39" s="2"/>
-      <c r="X39" s="3" t="str">
-        <v>USOSFR10</v>
-      </c>
+      <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="8"/>
       <c r="AI39" s="3"/>
@@ -970,9 +947,6 @@
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="Q40" s="2"/>
-      <c r="X40" t="str">
-        <v>USOSFR15</v>
-      </c>
       <c r="Y40" s="3"/>
       <c r="AI40" s="3"/>
     </row>
@@ -981,9 +955,6 @@
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="Q41" s="2"/>
-      <c r="X41" t="str">
-        <v>USOSFR20</v>
-      </c>
       <c r="AI41" s="3"/>
     </row>
     <row r="42" spans="3:37" x14ac:dyDescent="0.25">
@@ -991,9 +962,6 @@
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="Q42" s="2"/>
-      <c r="X42" t="str">
-        <v>USOSFR25</v>
-      </c>
       <c r="AI42" s="3"/>
     </row>
     <row r="43" spans="3:37" x14ac:dyDescent="0.25">
@@ -1001,9 +969,6 @@
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="Q43" s="2"/>
-      <c r="X43" t="str">
-        <v>USOSFR30</v>
-      </c>
       <c r="AI43" s="3"/>
     </row>
     <row r="44" spans="3:37" x14ac:dyDescent="0.25">
@@ -1011,9 +976,6 @@
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="Q44" s="2"/>
-      <c r="X44" t="str">
-        <v>USOSFR40</v>
-      </c>
       <c r="AI44" s="3"/>
     </row>
     <row r="45" spans="3:37" x14ac:dyDescent="0.25">
@@ -1062,22 +1024,22 @@
     </row>
     <row r="51" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
+      <c r="J51" s="17"/>
+      <c r="M51" s="11"/>
       <c r="Q51" s="2"/>
       <c r="AI51" s="13"/>
     </row>
     <row r="52" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
+      <c r="J52" s="16"/>
+      <c r="M52" s="11"/>
       <c r="Q52" s="2"/>
       <c r="AI52" s="3"/>
     </row>
     <row r="53" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
+      <c r="J53" s="16"/>
+      <c r="M53" s="11"/>
       <c r="Q53" s="2"/>
       <c r="AI53" s="3"/>
     </row>
@@ -1091,7 +1053,7 @@
     <row r="55" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C55" s="2"/>
       <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
+      <c r="J55" s="21"/>
       <c r="Q55" s="2"/>
       <c r="AI55" s="3"/>
     </row>
@@ -1103,6 +1065,7 @@
     <row r="57" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C57" s="2"/>
       <c r="I57" s="2"/>
+      <c r="L57" s="18"/>
       <c r="AI57" s="3"/>
     </row>
     <row r="58" spans="3:35" x14ac:dyDescent="0.25">
@@ -1121,6 +1084,7 @@
     <row r="61" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C61" s="2"/>
       <c r="I61" s="2"/>
+      <c r="L61" s="18"/>
     </row>
     <row r="62" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C62" s="2"/>
@@ -1129,6 +1093,7 @@
     <row r="63" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C63" s="2"/>
       <c r="I63" s="2"/>
+      <c r="L63" s="19"/>
     </row>
     <row r="64" spans="3:35" x14ac:dyDescent="0.25">
       <c r="C64" s="2"/>
